--- a/artfynd/A 65165-2021 artfynd.xlsx
+++ b/artfynd/A 65165-2021 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124678191</v>
+        <v>124678171</v>
       </c>
       <c r="B2" t="n">
-        <v>57529</v>
+        <v>96354</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,39 +691,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100049</v>
+        <v>53</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Fyrkanten, Upl</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>669961</v>
+        <v>669788</v>
       </c>
       <c r="R2" t="n">
-        <v>6694760</v>
+        <v>6694675</v>
       </c>
       <c r="S2" t="n">
         <v>15</v>
@@ -766,6 +761,21 @@
       </c>
       <c r="AG2" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ2" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK2" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO2" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
@@ -782,10 +792,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124678171</v>
+        <v>124678191</v>
       </c>
       <c r="B3" t="n">
-        <v>96354</v>
+        <v>57529</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -798,34 +808,39 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>53</v>
+        <v>100049</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Fyrkanten, Upl</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>669788</v>
+        <v>669961</v>
       </c>
       <c r="R3" t="n">
-        <v>6694675</v>
+        <v>6694760</v>
       </c>
       <c r="S3" t="n">
         <v>15</v>
@@ -868,21 +883,6 @@
       </c>
       <c r="AG3" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ3" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK3" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO3" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">

--- a/artfynd/A 65165-2021 artfynd.xlsx
+++ b/artfynd/A 65165-2021 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124678171</v>
+        <v>124678191</v>
       </c>
       <c r="B2" t="n">
-        <v>96354</v>
+        <v>57529</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,34 +691,39 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>53</v>
+        <v>100049</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Fyrkanten, Upl</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>669788</v>
+        <v>669961</v>
       </c>
       <c r="R2" t="n">
-        <v>6694675</v>
+        <v>6694760</v>
       </c>
       <c r="S2" t="n">
         <v>15</v>
@@ -761,21 +766,6 @@
       </c>
       <c r="AG2" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ2" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK2" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO2" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
@@ -792,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124678191</v>
+        <v>124678171</v>
       </c>
       <c r="B3" t="n">
-        <v>57529</v>
+        <v>96354</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -808,39 +798,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100049</v>
+        <v>53</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Fyrkanten, Upl</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>669961</v>
+        <v>669788</v>
       </c>
       <c r="R3" t="n">
-        <v>6694760</v>
+        <v>6694675</v>
       </c>
       <c r="S3" t="n">
         <v>15</v>
@@ -883,6 +868,21 @@
       </c>
       <c r="AG3" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ3" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK3" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO3" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">

--- a/artfynd/A 65165-2021 artfynd.xlsx
+++ b/artfynd/A 65165-2021 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>124678171</v>
       </c>
       <c r="B2" t="n">
-        <v>96354</v>
+        <v>96522</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>124678191</v>
       </c>
       <c r="B3" t="n">
-        <v>57529</v>
+        <v>57632</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>

--- a/artfynd/A 65165-2021 artfynd.xlsx
+++ b/artfynd/A 65165-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,12 +678,7 @@
         <v>124678171</v>
       </c>
       <c r="B2" t="n">
-        <v>96522</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97358</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -792,19 +787,14 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124678191</v>
+        <v>124678190</v>
       </c>
       <c r="B3" t="n">
-        <v>57632</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
@@ -837,10 +827,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>669961</v>
+        <v>669865</v>
       </c>
       <c r="R3" t="n">
-        <v>6694760</v>
+        <v>6694735</v>
       </c>
       <c r="S3" t="n">
         <v>15</v>
@@ -896,6 +886,108 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>124678191</v>
+      </c>
+      <c r="B4" t="n">
+        <v>57950</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Fyrkanten, Upl</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>669961</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6694760</v>
+      </c>
+      <c r="S4" t="n">
+        <v>15</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Valö</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2025-05-02</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2025-05-02</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Ingemar Södergren</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Ingemar Södergren</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 65165-2021 artfynd.xlsx
+++ b/artfynd/A 65165-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AZ4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -784,6 +789,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124678171</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -886,6 +896,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124678190</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -988,8 +1003,18 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124678191</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>